--- a/resources/templates/standard/H2100-02.xlsx
+++ b/resources/templates/standard/H2100-02.xlsx
@@ -94,7 +94,7 @@
 판매금액</t>
   </si>
   <si>
-    <t>원소재+삼보매출액</t>
+    <t>원소재+고객사 매출액</t>
   </si>
   <si>
     <t>융진 매출누계</t>

--- a/resources/templates/standard/H2100-02.xlsx
+++ b/resources/templates/standard/H2100-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>월 납품량 분석 보고서 ( 00월 )</t>
   </si>
@@ -1048,7 +1051,9 @@
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="1.625" customHeight="1"/>
   <sheetData>
     <row r="1" ht="4.5" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1197,7 +1202,7 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
@@ -1282,12 +1287,12 @@
       <c r="CQ2" s="7"/>
       <c r="CR2" s="7"/>
       <c r="CS2" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CT2" s="8"/>
       <c r="CU2" s="8"/>
       <c r="CV2" s="9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW2" s="9"/>
       <c r="CX2" s="9"/>
@@ -1296,7 +1301,7 @@
       <c r="DA2" s="9"/>
       <c r="DB2" s="9"/>
       <c r="DC2" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DD2" s="9"/>
       <c r="DE2" s="9"/>
@@ -1305,7 +1310,7 @@
       <c r="DH2" s="9"/>
       <c r="DI2" s="9"/>
       <c r="DJ2" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DK2" s="9"/>
       <c r="DL2" s="9"/>
@@ -1599,7 +1604,7 @@
     </row>
     <row r="5" ht="25.5" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1871,7 +1876,7 @@
     </row>
     <row r="7" ht="23.45" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -2040,13 +2045,13 @@
     </row>
     <row r="8" ht="23.45" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
       <c r="E8" s="17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
@@ -2183,7 +2188,7 @@
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
@@ -2320,7 +2325,7 @@
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
@@ -2457,7 +2462,7 @@
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
@@ -2592,13 +2597,13 @@
     </row>
     <row r="12" ht="23.45" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A12" s="31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="E12" s="32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -2735,7 +2740,7 @@
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
       <c r="E13" s="32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -2872,7 +2877,7 @@
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
       <c r="E14" s="35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" s="35"/>
       <c r="G14" s="35"/>
@@ -3009,7 +3014,7 @@
       <c r="C15" s="31"/>
       <c r="D15" s="31"/>
       <c r="E15" s="39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
@@ -3144,7 +3149,7 @@
     </row>
     <row r="16" ht="23.45" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A16" s="43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
@@ -3281,7 +3286,7 @@
     </row>
     <row r="17" ht="23.45" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A17" s="47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="47"/>
       <c r="C17" s="47"/>
@@ -3585,7 +3590,7 @@
     </row>
     <row r="19" ht="23.45" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -3752,13 +3757,13 @@
     </row>
     <row r="20" ht="23.45" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
       <c r="E20" s="17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
@@ -3895,7 +3900,7 @@
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
@@ -4032,7 +4037,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
@@ -4169,7 +4174,7 @@
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
       <c r="E23" s="26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
@@ -4304,13 +4309,13 @@
     </row>
     <row r="24" ht="23.45" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
       <c r="E24" s="32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="32"/>
@@ -4447,7 +4452,7 @@
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
       <c r="E25" s="32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -4584,7 +4589,7 @@
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
       <c r="E26" s="35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F26" s="35"/>
       <c r="G26" s="35"/>
@@ -4721,7 +4726,7 @@
       <c r="C27" s="31"/>
       <c r="D27" s="31"/>
       <c r="E27" s="39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F27" s="39"/>
       <c r="G27" s="39"/>
@@ -4856,7 +4861,7 @@
     </row>
     <row r="28" ht="23.45" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A28" s="43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B28" s="43"/>
       <c r="C28" s="43"/>
@@ -4993,7 +4998,7 @@
     </row>
     <row r="29" ht="23.45" customHeight="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A29" s="47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B29" s="47"/>
       <c r="C29" s="47"/>
@@ -5284,7 +5289,7 @@
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
       <c r="R31" s="51" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S31" s="51"/>
       <c r="T31" s="51"/>
@@ -5308,7 +5313,7 @@
       <c r="AL31" s="52"/>
       <c r="AM31" s="2"/>
       <c r="AN31" s="53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO31" s="53"/>
       <c r="AP31" s="53"/>
@@ -5341,7 +5346,7 @@
       <c r="BQ31" s="54"/>
       <c r="BR31" s="2"/>
       <c r="BS31" s="51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BT31" s="51"/>
       <c r="BU31" s="51"/>
@@ -5365,7 +5370,7 @@
       <c r="CM31" s="55"/>
       <c r="CN31" s="56"/>
       <c r="CO31" s="57" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CP31" s="57"/>
       <c r="CQ31" s="57"/>
@@ -5427,7 +5432,7 @@
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
       <c r="R32" s="51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S32" s="51"/>
       <c r="T32" s="51"/>
@@ -5451,7 +5456,7 @@
       <c r="AL32" s="52"/>
       <c r="AM32" s="2"/>
       <c r="AN32" s="59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO32" s="59"/>
       <c r="AP32" s="59"/>
@@ -5484,7 +5489,7 @@
       <c r="BQ32" s="60"/>
       <c r="BR32" s="2"/>
       <c r="BS32" s="51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BT32" s="51"/>
       <c r="BU32" s="51"/>
@@ -5703,7 +5708,7 @@
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="61" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S34" s="61"/>
       <c r="T34" s="61"/>
@@ -5727,7 +5732,7 @@
       <c r="AL34" s="62"/>
       <c r="AM34" s="2"/>
       <c r="AN34" s="53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO34" s="53"/>
       <c r="AP34" s="53"/>
@@ -5760,7 +5765,7 @@
       <c r="BQ34" s="54"/>
       <c r="BR34" s="2"/>
       <c r="BS34" s="63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BT34" s="63"/>
       <c r="BU34" s="63"/>
@@ -5784,7 +5789,7 @@
       <c r="CM34" s="64"/>
       <c r="CN34" s="2"/>
       <c r="CO34" s="65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CP34" s="65"/>
       <c r="CQ34" s="65"/>
@@ -5868,7 +5873,7 @@
       <c r="AL35" s="62"/>
       <c r="AM35" s="2"/>
       <c r="AN35" s="59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO35" s="59"/>
       <c r="AP35" s="59"/>
